--- a/Listing/MBF04S.xlsx
+++ b/Listing/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="409">
   <si>
     <t/>
   </si>
@@ -49,64 +49,469 @@
     <t>3</t>
   </si>
   <si>
-    <t>20004386</t>
-  </si>
-  <si>
-    <t>NESTLE WRT BYM LB120</t>
+    <t>10003111</t>
+  </si>
+  <si>
+    <t>PROMINA BB MARI S150</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20034046</t>
+  </si>
+  <si>
+    <t>SUN MARIE BISC BLT80</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20134698</t>
+  </si>
+  <si>
+    <t>SUN MARIE BISC KJU80</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20032058</t>
+  </si>
+  <si>
+    <t>FF KENTAL MANIS 6X37</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10015124</t>
+  </si>
+  <si>
+    <t>FF SKM COKLAT 6X37</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20013435</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS PUTIH 6'S</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20013434</t>
+  </si>
+  <si>
+    <t>INDOMILK SKM CKT6X37</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20013433</t>
+  </si>
+  <si>
+    <t>INDOMILK SKM PTH6X37</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>10000724</t>
+  </si>
+  <si>
+    <t>SUN BBR SS BRS/M 120</t>
+  </si>
+  <si>
+    <t>10031256</t>
+  </si>
+  <si>
+    <t>SUN BBR SS AYM&amp;B 120</t>
+  </si>
+  <si>
+    <t>20073496</t>
+  </si>
+  <si>
+    <t>SUN BBR SS UBI/U120G</t>
+  </si>
+  <si>
+    <t>10022197</t>
+  </si>
+  <si>
+    <t>SUN BBR.PISANG SC120</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20032058</t>
-  </si>
-  <si>
-    <t>FF KENTAL MANIS 6X37</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10015124</t>
-  </si>
-  <si>
-    <t>FF SKM COKLAT 6X37</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20013435</t>
-  </si>
-  <si>
-    <t>ENAK K/MNS PUTIH 6'S</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20013434</t>
-  </si>
-  <si>
-    <t>INDOMILK SKM CKT6X37</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20013433</t>
-  </si>
-  <si>
-    <t>INDOMILK SKM PTH6X37</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>10000146</t>
+  </si>
+  <si>
+    <t>SUN KC HIJAU EKO 120</t>
+  </si>
+  <si>
+    <t>10000143</t>
+  </si>
+  <si>
+    <t>SUN BRS MERAH EKO120</t>
+  </si>
+  <si>
+    <t>20001705</t>
+  </si>
+  <si>
+    <t>MILNA BISC.6+ PSG110</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20001701</t>
+  </si>
+  <si>
+    <t>MILNA BISC.6+ ORG110</t>
+  </si>
+  <si>
+    <t>10010825</t>
+  </si>
+  <si>
+    <t>MLNA WGAN AYM+KP 120</t>
+  </si>
+  <si>
+    <t>10000720</t>
+  </si>
+  <si>
+    <t>PROMINA TIM SP&amp;WR120</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10003707</t>
+  </si>
+  <si>
+    <t>PROMINA C.CHKN BR120</t>
+  </si>
+  <si>
+    <t>10021949</t>
+  </si>
+  <si>
+    <t>PROMINA DGNG&amp;BRO 100</t>
+  </si>
+  <si>
+    <t>20012830</t>
+  </si>
+  <si>
+    <t>PRMNA TIM AYM KP 100</t>
+  </si>
+  <si>
+    <t>20002201</t>
+  </si>
+  <si>
+    <t>PROMINA AYM,T,W 100G</t>
+  </si>
+  <si>
+    <t>20012831</t>
+  </si>
+  <si>
+    <t>PROMINA TIM SLMON100</t>
+  </si>
+  <si>
+    <t>10033560</t>
+  </si>
+  <si>
+    <t>PROMINA CHO.AVCD 100</t>
+  </si>
+  <si>
+    <t>20139959</t>
+  </si>
+  <si>
+    <t>PRMN SALMON LM 120G</t>
+  </si>
+  <si>
+    <t>20100805</t>
+  </si>
+  <si>
+    <t>PRMNA PUDNG CHO 4X25</t>
+  </si>
+  <si>
+    <t>20067680</t>
+  </si>
+  <si>
+    <t>PRMNA PUDNG STRW 100</t>
+  </si>
+  <si>
+    <t>20113322</t>
+  </si>
+  <si>
+    <t>PROMINA PASTA M&amp;C 70</t>
+  </si>
+  <si>
+    <t>20126004</t>
+  </si>
+  <si>
+    <t>PROMINA PASTA CCS 60</t>
+  </si>
+  <si>
+    <t>20126003</t>
+  </si>
+  <si>
+    <t>PRMNA MI BT AYM KP75</t>
+  </si>
+  <si>
+    <t>20135120</t>
+  </si>
+  <si>
+    <t>PRMNA SFTCRN BUTER15</t>
+  </si>
+  <si>
+    <t>10025325</t>
+  </si>
+  <si>
+    <t>PRMNA SUPMI AYM SY81</t>
+  </si>
+  <si>
+    <t>10025326</t>
+  </si>
+  <si>
+    <t>PRMN SUPMI DG&amp;SYR 84</t>
+  </si>
+  <si>
+    <t>20094437</t>
+  </si>
+  <si>
+    <t>PROMINA CRUNCHIES 20</t>
+  </si>
+  <si>
+    <t>20129287</t>
+  </si>
+  <si>
+    <t>PRMINA CRN SEAWED 20</t>
+  </si>
+  <si>
+    <t>20129288</t>
+  </si>
+  <si>
+    <t>PRMINA CRN CHKN.BR20</t>
+  </si>
+  <si>
+    <t>20136087</t>
+  </si>
+  <si>
+    <t>PRMNA SFTCRN STRWB15</t>
+  </si>
+  <si>
+    <t>20141387</t>
+  </si>
+  <si>
+    <t>PROMINA MC CHO.AL 42</t>
+  </si>
+  <si>
+    <t>20141376</t>
+  </si>
+  <si>
+    <t>PROMINA MC BL.CHS 42</t>
+  </si>
+  <si>
+    <t>20133324</t>
+  </si>
+  <si>
+    <t>PRMINA CRCKR BRCLI20</t>
+  </si>
+  <si>
+    <t>20134695</t>
+  </si>
+  <si>
+    <t>PRMNA CRCKR BRRIES20</t>
+  </si>
+  <si>
+    <t>20077368</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF BNANA 15</t>
+  </si>
+  <si>
+    <t>20077369</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF BLUBR 15</t>
+  </si>
+  <si>
+    <t>20092042</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF STRWAP15</t>
+  </si>
+  <si>
+    <t>20139421</t>
+  </si>
+  <si>
+    <t>PRMINA YGR MLT SRW 8</t>
+  </si>
+  <si>
+    <t>20139431</t>
+  </si>
+  <si>
+    <t>PRMINA YGR MLT MLK 8</t>
+  </si>
+  <si>
+    <t>20109115</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG BNN15</t>
+  </si>
+  <si>
+    <t>20103062</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG AMB15</t>
+  </si>
+  <si>
+    <t>20103061</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG CHS15</t>
+  </si>
+  <si>
+    <t>20027865</t>
+  </si>
+  <si>
+    <t>MILNA SUP AYM JG 100</t>
+  </si>
+  <si>
+    <t>20027867</t>
+  </si>
+  <si>
+    <t>MILNA ATI AYM BYM120</t>
+  </si>
+  <si>
+    <t>20122054</t>
+  </si>
+  <si>
+    <t>MLNA BBR SLMN CB 100</t>
+  </si>
+  <si>
+    <t>20138171</t>
+  </si>
+  <si>
+    <t>PRMN MELTY B.STRW 42</t>
+  </si>
+  <si>
+    <t>20137013</t>
+  </si>
+  <si>
+    <t>MILNA CRNCH CHSE 20G</t>
+  </si>
+  <si>
+    <t>20115159</t>
+  </si>
+  <si>
+    <t>MLNA RC.CRAC BNANA20</t>
+  </si>
+  <si>
+    <t>20115158</t>
+  </si>
+  <si>
+    <t>MLNA RC.CRACK SPC 20</t>
+  </si>
+  <si>
+    <t>20092863</t>
+  </si>
+  <si>
+    <t>YB BABY CRCK STRW 25</t>
+  </si>
+  <si>
+    <t>20080924</t>
+  </si>
+  <si>
+    <t>YB BABY CRACK BNN 25</t>
+  </si>
+  <si>
+    <t>20138661</t>
+  </si>
+  <si>
+    <t>BROMON CKS MIX.F 100</t>
+  </si>
+  <si>
+    <t>20138660</t>
+  </si>
+  <si>
+    <t>BOROMON CKS MILK 100</t>
+  </si>
+  <si>
+    <t>20141377</t>
+  </si>
+  <si>
+    <t>PROMNA PSTA BLOGNESE</t>
+  </si>
+  <si>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
+  </si>
+  <si>
+    <t>20118115</t>
+  </si>
+  <si>
+    <t>FRISIAN FLAG PTH 240</t>
+  </si>
+  <si>
+    <t>20112945</t>
+  </si>
+  <si>
+    <t>FF SKM COKLAT 240G</t>
+  </si>
+  <si>
+    <t>20121733</t>
+  </si>
+  <si>
+    <t>FF GOLD SKM PTH 240G</t>
+  </si>
+  <si>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
+  </si>
+  <si>
+    <t>20120855</t>
+  </si>
+  <si>
+    <t>INDOMILK SWIS CHO535</t>
+  </si>
+  <si>
+    <t>20125783</t>
+  </si>
+  <si>
+    <t>CAP/ENAK KKM PTH 535</t>
+  </si>
+  <si>
+    <t>20141099</t>
+  </si>
+  <si>
+    <t>FF CRMY GULA ARN 240</t>
+  </si>
+  <si>
+    <t>20105631</t>
+  </si>
+  <si>
+    <t>CARNATION KKM 405G</t>
   </si>
   <si>
     <t>20101859</t>
@@ -115,334 +520,52 @@
     <t>SUNBAY EVP.MILK 380G</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20105631</t>
-  </si>
-  <si>
-    <t>CARNATION KKM 405G</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>10000724</t>
-  </si>
-  <si>
-    <t>SUN BBR SS BRS/M 120</t>
-  </si>
-  <si>
-    <t>10031256</t>
-  </si>
-  <si>
-    <t>SUN BBR SS AYM&amp;B 120</t>
-  </si>
-  <si>
-    <t>10037727</t>
-  </si>
-  <si>
-    <t>SUN BBR SS PSNG 120G</t>
-  </si>
-  <si>
-    <t>20073496</t>
-  </si>
-  <si>
-    <t>SUN BBR SS UBI/U120G</t>
-  </si>
-  <si>
-    <t>10022197</t>
-  </si>
-  <si>
-    <t>SUN BBR.PISANG SC120</t>
-  </si>
-  <si>
-    <t>10000146</t>
-  </si>
-  <si>
-    <t>SUN KC HIJAU EKO 120</t>
-  </si>
-  <si>
-    <t>10000143</t>
-  </si>
-  <si>
-    <t>SUN BRS MERAH EKO120</t>
-  </si>
-  <si>
-    <t>20027865</t>
-  </si>
-  <si>
-    <t>MILNA SUP AYM JG 100</t>
-  </si>
-  <si>
-    <t>20027867</t>
-  </si>
-  <si>
-    <t>MILNA ATI AYM BYM120</t>
-  </si>
-  <si>
-    <t>20122054</t>
-  </si>
-  <si>
-    <t>MLNA BBR SLMN CB 100</t>
-  </si>
-  <si>
-    <t>20139959</t>
-  </si>
-  <si>
-    <t>PRMN SALMON LM 120G</t>
-  </si>
-  <si>
-    <t>10000720</t>
-  </si>
-  <si>
-    <t>PROMINA TIM SP&amp;WR120</t>
-  </si>
-  <si>
-    <t>10003707</t>
-  </si>
-  <si>
-    <t>PROMINA C.CHKN BR120</t>
-  </si>
-  <si>
-    <t>10021949</t>
-  </si>
-  <si>
-    <t>PROMINA DGNG&amp;BRO 100</t>
-  </si>
-  <si>
-    <t>20012830</t>
-  </si>
-  <si>
-    <t>PRMNA TIM AYM KP 100</t>
-  </si>
-  <si>
-    <t>20002201</t>
-  </si>
-  <si>
-    <t>PROMINA AYM,T,W 100G</t>
-  </si>
-  <si>
-    <t>20012831</t>
-  </si>
-  <si>
-    <t>PROMINA TIM SLMON100</t>
-  </si>
-  <si>
-    <t>10033560</t>
-  </si>
-  <si>
-    <t>PROMINA CHO.AVCD 100</t>
-  </si>
-  <si>
-    <t>10003111</t>
-  </si>
-  <si>
-    <t>PROMINA BB MARI S150</t>
-  </si>
-  <si>
-    <t>20034046</t>
-  </si>
-  <si>
-    <t>SUN MARIE BISC BLT80</t>
-  </si>
-  <si>
-    <t>20134698</t>
-  </si>
-  <si>
-    <t>SUN MARIE BISC KJU80</t>
-  </si>
-  <si>
-    <t>20001705</t>
-  </si>
-  <si>
-    <t>MILNA BISC.6+ PSG110</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20001701</t>
-  </si>
-  <si>
-    <t>MILNA BISC.6+ ORG110</t>
-  </si>
-  <si>
-    <t>20100805</t>
-  </si>
-  <si>
-    <t>PRMNA PUDNG CHO 4X25</t>
-  </si>
-  <si>
-    <t>20067680</t>
-  </si>
-  <si>
-    <t>PRMNA PUDNG STRW 100</t>
-  </si>
-  <si>
-    <t>10010825</t>
-  </si>
-  <si>
-    <t>MLNA WGAN AYM+KP 120</t>
-  </si>
-  <si>
-    <t>20138171</t>
-  </si>
-  <si>
-    <t>PRMN MELTY B.STRW 42</t>
-  </si>
-  <si>
-    <t>20136087</t>
-  </si>
-  <si>
-    <t>PRMNA SFTCRN STRWB15</t>
-  </si>
-  <si>
-    <t>20135120</t>
-  </si>
-  <si>
-    <t>PRMNA SFTCRN BUTER15</t>
-  </si>
-  <si>
-    <t>20113322</t>
-  </si>
-  <si>
-    <t>PROMINA PASTA M&amp;C 70</t>
-  </si>
-  <si>
-    <t>20126004</t>
-  </si>
-  <si>
-    <t>PROMINA PASTA CCS 60</t>
-  </si>
-  <si>
-    <t>20126003</t>
-  </si>
-  <si>
-    <t>PRMNA MI BT AYM KP75</t>
-  </si>
-  <si>
-    <t>10025326</t>
-  </si>
-  <si>
-    <t>PRMN SUPMI DG&amp;SYR 84</t>
-  </si>
-  <si>
-    <t>10025325</t>
-  </si>
-  <si>
-    <t>PRMNA SUPMI AYM SY81</t>
-  </si>
-  <si>
-    <t>20077368</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF BNANA 15</t>
-  </si>
-  <si>
-    <t>20077369</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF BLUBR 15</t>
-  </si>
-  <si>
-    <t>20092042</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF STRWAP15</t>
-  </si>
-  <si>
-    <t>20094437</t>
-  </si>
-  <si>
-    <t>PROMINA CRUNCHIES 20</t>
-  </si>
-  <si>
-    <t>20129287</t>
-  </si>
-  <si>
-    <t>PRMINA CRN SEAWED 20</t>
-  </si>
-  <si>
-    <t>20129288</t>
-  </si>
-  <si>
-    <t>PRMINA CRN CHKN.BR20</t>
-  </si>
-  <si>
-    <t>20133324</t>
-  </si>
-  <si>
-    <t>PRMINA CRCKR BRCLI20</t>
-  </si>
-  <si>
-    <t>20134695</t>
-  </si>
-  <si>
-    <t>PRMNA CRCKR BRRIES20</t>
-  </si>
-  <si>
-    <t>20137013</t>
-  </si>
-  <si>
-    <t>MILNA CRNCH CHSE 20G</t>
-  </si>
-  <si>
-    <t>20109115</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG BNN15</t>
-  </si>
-  <si>
-    <t>20103062</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG AMB15</t>
-  </si>
-  <si>
-    <t>20103061</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG CHS15</t>
-  </si>
-  <si>
-    <t>20115159</t>
-  </si>
-  <si>
-    <t>MLNA RC.CRAC BNANA20</t>
-  </si>
-  <si>
-    <t>20115158</t>
-  </si>
-  <si>
-    <t>MLNA RC.CRACK SPC 20</t>
-  </si>
-  <si>
-    <t>20092863</t>
-  </si>
-  <si>
-    <t>YB BABY CRCK STRW 25</t>
-  </si>
-  <si>
-    <t>20080924</t>
-  </si>
-  <si>
-    <t>YB BABY CRACK BNN 25</t>
-  </si>
-  <si>
-    <t>20138661</t>
-  </si>
-  <si>
-    <t>BROMON CKS MIX.F 100</t>
-  </si>
-  <si>
-    <t>20138660</t>
-  </si>
-  <si>
-    <t>BOROMON CKS MILK 100</t>
+    <t>10005489</t>
+  </si>
+  <si>
+    <t>FF KENTAL MANIS 370G</t>
+  </si>
+  <si>
+    <t>10000255</t>
+  </si>
+  <si>
+    <t>FF GOLD SKM PTH 370G</t>
+  </si>
+  <si>
+    <t>20089819</t>
+  </si>
+  <si>
+    <t>FF KENTAL MANIS 490G</t>
+  </si>
+  <si>
+    <t>10000088</t>
+  </si>
+  <si>
+    <t>FF SKM CKLT KLG 370</t>
+  </si>
+  <si>
+    <t>20136704</t>
+  </si>
+  <si>
+    <t>INDOMLK KM DURIAN370</t>
+  </si>
+  <si>
+    <t>10031572</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS COKLT370G</t>
+  </si>
+  <si>
+    <t>10000021</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS PUTIH 370</t>
+  </si>
+  <si>
+    <t>10036665</t>
+  </si>
+  <si>
+    <t>CARNATION KKM 365G</t>
   </si>
   <si>
     <t>20002313</t>
@@ -457,115 +580,208 @@
     <t>3SAPI KRIMER 490G</t>
   </si>
   <si>
-    <t>10036665</t>
-  </si>
-  <si>
-    <t>CARNATION KKM 365G</t>
-  </si>
-  <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535G</t>
-  </si>
-  <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535G</t>
-  </si>
-  <si>
-    <t>20118115</t>
-  </si>
-  <si>
-    <t>FRISIAN FLAG PTH 240</t>
-  </si>
-  <si>
-    <t>20112945</t>
-  </si>
-  <si>
-    <t>FF SKM COKLAT 240G</t>
-  </si>
-  <si>
-    <t>20121733</t>
-  </si>
-  <si>
-    <t>FF GOLD SKM PTH 240G</t>
-  </si>
-  <si>
-    <t>20132814</t>
-  </si>
-  <si>
-    <t>FF SKM KRN.STRWB 260</t>
-  </si>
-  <si>
-    <t>20094283</t>
-  </si>
-  <si>
-    <t>INDOMILK KM PTH 545G</t>
-  </si>
-  <si>
-    <t>20120855</t>
-  </si>
-  <si>
-    <t>INDOMILK SWIS CHO545</t>
-  </si>
-  <si>
-    <t>20125783</t>
-  </si>
-  <si>
-    <t>CAP/ENAK KKM PTH 545</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>10005489</t>
-  </si>
-  <si>
-    <t>FF KENTAL MANIS 370G</t>
-  </si>
-  <si>
-    <t>10000255</t>
-  </si>
-  <si>
-    <t>FF GOLD SKM PTH 370G</t>
-  </si>
-  <si>
-    <t>20089819</t>
-  </si>
-  <si>
-    <t>FF KENTAL MANIS 490G</t>
-  </si>
-  <si>
-    <t>10000088</t>
-  </si>
-  <si>
-    <t>FF SKM CKLT KLG 370</t>
-  </si>
-  <si>
-    <t>10000019</t>
-  </si>
-  <si>
-    <t>INDOMILK SKM PTH 370</t>
-  </si>
-  <si>
-    <t>20136704</t>
-  </si>
-  <si>
-    <t>INDOMLK KM DURIAN370</t>
-  </si>
-  <si>
-    <t>10031572</t>
-  </si>
-  <si>
-    <t>ENAK K/MNS COKLT370G</t>
-  </si>
-  <si>
-    <t>10000021</t>
-  </si>
-  <si>
-    <t>ENAK K/MNS PUTIH 370</t>
+    <t>10003653</t>
+  </si>
+  <si>
+    <t>MRINAGA BMT1 LAC.390</t>
+  </si>
+  <si>
+    <t>20014399</t>
+  </si>
+  <si>
+    <t>MORINAGA CK3 VAN 780</t>
+  </si>
+  <si>
+    <t>10005241</t>
+  </si>
+  <si>
+    <t>MORINAGA CM ORGN 190</t>
+  </si>
+  <si>
+    <t>10008314</t>
+  </si>
+  <si>
+    <t>MORINAGA CK VNLA 190</t>
+  </si>
+  <si>
+    <t>10008316</t>
+  </si>
+  <si>
+    <t>MORINAGA CK MADU 190</t>
+  </si>
+  <si>
+    <t>20098370</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU350</t>
+  </si>
+  <si>
+    <t>20098369</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ VAN350</t>
+  </si>
+  <si>
+    <t>20135200</t>
+  </si>
+  <si>
+    <t>VIDORAN BABY0-6 575G</t>
+  </si>
+  <si>
+    <t>20129773</t>
+  </si>
+  <si>
+    <t>VDORAN BABY6-12 575G</t>
+  </si>
+  <si>
+    <t>20117983</t>
+  </si>
+  <si>
+    <t>VIDORAN XM5+ COKL700</t>
+  </si>
+  <si>
+    <t>20070110</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU700</t>
+  </si>
+  <si>
+    <t>20090042</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ VAN700</t>
+  </si>
+  <si>
+    <t>20082394</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ MDU700</t>
+  </si>
+  <si>
+    <t>20090437</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ VAN700</t>
+  </si>
+  <si>
+    <t>20117985</t>
+  </si>
+  <si>
+    <t>VIDORAN XM5+ MADU700</t>
+  </si>
+  <si>
+    <t>20113346</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ VAN 900</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20101825</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ MDU 900</t>
+  </si>
+  <si>
+    <t>20106381</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT3+ MDU 900</t>
+  </si>
+  <si>
+    <t>20117981</t>
+  </si>
+  <si>
+    <t>VIDORAN XM3+ VNL900</t>
+  </si>
+  <si>
+    <t>20138473</t>
+  </si>
+  <si>
+    <t>VDORAN BABY6-12 900G</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20138474</t>
+  </si>
+  <si>
+    <t>VIDORAN 5  MADU 900G</t>
+  </si>
+  <si>
+    <t>20125790</t>
+  </si>
+  <si>
+    <t>HLTHYWY3+ SB MADU700</t>
+  </si>
+  <si>
+    <t>20125788</t>
+  </si>
+  <si>
+    <t>HLTHYWY1+ SP MADU700</t>
+  </si>
+  <si>
+    <t>20136510</t>
+  </si>
+  <si>
+    <t>MILO 3IN1 ACT-GO 400</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20027850</t>
+  </si>
+  <si>
+    <t>ZEE VNILA TWST 340G</t>
+  </si>
+  <si>
+    <t>20027848</t>
+  </si>
+  <si>
+    <t>ZEE SWIZZ CHO 340G</t>
+  </si>
+  <si>
+    <t>20033353</t>
+  </si>
+  <si>
+    <t>HILO/S HI-CAL CHO250</t>
+  </si>
+  <si>
+    <t>10000578</t>
+  </si>
+  <si>
+    <t>DIABETASOL VNL.170GR</t>
+  </si>
+  <si>
+    <t>20021571</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD VAN 570G</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>10020147</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD CKLT 230</t>
+  </si>
+  <si>
+    <t>10008064</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD ORG240G</t>
+  </si>
+  <si>
+    <t>10012172</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD VNLA 230</t>
   </si>
   <si>
     <t>20087580</t>
@@ -580,187 +796,187 @@
     <t>ENTRASOL GOLD VAN170</t>
   </si>
   <si>
-    <t>20021571</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VAN 570G</t>
-  </si>
-  <si>
-    <t>10020147</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD CKLT 230</t>
-  </si>
-  <si>
-    <t>10008064</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD ORG240G</t>
-  </si>
-  <si>
-    <t>10012198</t>
-  </si>
-  <si>
-    <t>ANLENE ACTF VNL 230G</t>
-  </si>
-  <si>
-    <t>10012172</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VNLA 230</t>
-  </si>
-  <si>
-    <t>10000578</t>
-  </si>
-  <si>
-    <t>DIABETASOL VNL.170GR</t>
-  </si>
-  <si>
-    <t>20098371</t>
-  </si>
-  <si>
-    <t>VDORAN SUSU MADU 350</t>
-  </si>
-  <si>
-    <t>20098369</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ VAN350</t>
-  </si>
-  <si>
-    <t>20138473</t>
-  </si>
-  <si>
-    <t>VDORAN BABY6-12 925G</t>
-  </si>
-  <si>
-    <t>20117981</t>
-  </si>
-  <si>
-    <t>VIDORAN XM3+ VNL925</t>
-  </si>
-  <si>
-    <t>20138474</t>
-  </si>
-  <si>
-    <t>VIDORAN 5  MADU 925G</t>
-  </si>
-  <si>
-    <t>20070110</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU700</t>
-  </si>
-  <si>
-    <t>20090042</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ VAN700</t>
-  </si>
-  <si>
-    <t>20082394</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ MDU700</t>
-  </si>
-  <si>
-    <t>20090437</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ VAN700</t>
-  </si>
-  <si>
-    <t>20117985</t>
-  </si>
-  <si>
-    <t>VIDORAN XM5+ MADU700</t>
-  </si>
-  <si>
-    <t>20098370</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU350</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20098368</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ VAN350</t>
-  </si>
-  <si>
-    <t>20113346</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ VAN 925</t>
-  </si>
-  <si>
-    <t>20101825</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ MDU 925</t>
-  </si>
-  <si>
-    <t>20106381</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT3+ MDU 925</t>
-  </si>
-  <si>
-    <t>20135200</t>
-  </si>
-  <si>
-    <t>VIDORAN BABY0-6 575G</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20129773</t>
-  </si>
-  <si>
-    <t>VDORAN BABY6-12 575G</t>
-  </si>
-  <si>
-    <t>20117983</t>
-  </si>
-  <si>
-    <t>VIDORAN XM5+ COKL700</t>
-  </si>
-  <si>
-    <t>20125788</t>
-  </si>
-  <si>
-    <t>HLTHYWY1+ SP MADU725</t>
-  </si>
-  <si>
-    <t>20125790</t>
-  </si>
-  <si>
-    <t>HLTHYWY3+ SB MADU725</t>
-  </si>
-  <si>
-    <t>20027850</t>
-  </si>
-  <si>
-    <t>ZEE VNILA TWST 340G</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20027848</t>
-  </si>
-  <si>
-    <t>ZEE SWIZZ CHO 340G</t>
-  </si>
-  <si>
-    <t>20033353</t>
-  </si>
-  <si>
-    <t>HILO/S HI-CAL CHO250</t>
+    <t>10026038</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 150</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20040575</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 150G</t>
+  </si>
+  <si>
+    <t>20056930</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 150</t>
+  </si>
+  <si>
+    <t>20040299</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 400</t>
+  </si>
+  <si>
+    <t>20040302</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 400</t>
+  </si>
+  <si>
+    <t>20040301</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 400G</t>
+  </si>
+  <si>
+    <t>20040303</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ CKLT 400</t>
+  </si>
+  <si>
+    <t>20040340</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 400G</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20040312</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 400G</t>
+  </si>
+  <si>
+    <t>20040300</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 400G</t>
+  </si>
+  <si>
+    <t>20037098</t>
+  </si>
+  <si>
+    <t>SGM SOYA 1+ VANL 400</t>
+  </si>
+  <si>
+    <t>20087025</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 600G</t>
+  </si>
+  <si>
+    <t>20087024</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 600</t>
+  </si>
+  <si>
+    <t>20047323</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 550G</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20047324</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 550G</t>
+  </si>
+  <si>
+    <t>20074147</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 600</t>
+  </si>
+  <si>
+    <t>20077508</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 600G</t>
+  </si>
+  <si>
+    <t>20040294</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 900</t>
+  </si>
+  <si>
+    <t>10005279</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 150G</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20040293</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 900G</t>
+  </si>
+  <si>
+    <t>20040296</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 900</t>
+  </si>
+  <si>
+    <t>20040295</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 900G</t>
+  </si>
+  <si>
+    <t>20066494</t>
+  </si>
+  <si>
+    <t>SGM EKSPL5+ MADU 900</t>
+  </si>
+  <si>
+    <t>10005315</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 150G</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20040297</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 1KG</t>
+  </si>
+  <si>
+    <t>20040298</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 1KG</t>
+  </si>
+  <si>
+    <t>20065379</t>
+  </si>
+  <si>
+    <t>SGM SOYA1+ VANL 700G</t>
+  </si>
+  <si>
+    <t>20071686</t>
+  </si>
+  <si>
+    <t>SGM SOYA1+ MADU 700G</t>
   </si>
   <si>
     <t>20011063</t>
@@ -769,238 +985,175 @@
     <t>PRENAGEN HML CHO 360</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>10033006</t>
   </si>
   <si>
     <t>PRENAGEN HML CHO 180</t>
   </si>
   <si>
-    <t>20136510</t>
-  </si>
-  <si>
-    <t>MILO 3IN1 ACT-GO 400</t>
-  </si>
-  <si>
-    <t>20095418</t>
-  </si>
-  <si>
-    <t>MILO ACTIVE-GO 10'S</t>
-  </si>
-  <si>
-    <t>10003653</t>
-  </si>
-  <si>
-    <t>MRINAGA BMT1 LAC.390</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20014399</t>
-  </si>
-  <si>
-    <t>MORINAGA CK3 VAN 780</t>
-  </si>
-  <si>
-    <t>10005241</t>
-  </si>
-  <si>
-    <t>MORINAGA CM ORGN 190</t>
-  </si>
-  <si>
-    <t>10008314</t>
-  </si>
-  <si>
-    <t>MORINAGA CK VNLA 190</t>
-  </si>
-  <si>
-    <t>10008316</t>
-  </si>
-  <si>
-    <t>MORINAGA CK MADU 190</t>
-  </si>
-  <si>
-    <t>10026038</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 150</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20040575</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 150G</t>
-  </si>
-  <si>
-    <t>20056930</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 150</t>
-  </si>
-  <si>
-    <t>20040299</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 400</t>
-  </si>
-  <si>
-    <t>20040302</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 400</t>
-  </si>
-  <si>
-    <t>20040301</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 400G</t>
-  </si>
-  <si>
-    <t>20040303</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ CKLT 400</t>
-  </si>
-  <si>
-    <t>20040340</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 400G</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20040312</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 400G</t>
-  </si>
-  <si>
-    <t>20040300</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 400G</t>
-  </si>
-  <si>
-    <t>20037098</t>
-  </si>
-  <si>
-    <t>SGM SOYA 1+ VANL 400</t>
-  </si>
-  <si>
-    <t>20087025</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 600G</t>
-  </si>
-  <si>
-    <t>20087024</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 600</t>
-  </si>
-  <si>
-    <t>20047323</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 550G</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20047324</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 550G</t>
-  </si>
-  <si>
-    <t>20074147</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 600</t>
-  </si>
-  <si>
-    <t>20077508</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 600G</t>
-  </si>
-  <si>
-    <t>20040294</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 900</t>
-  </si>
-  <si>
-    <t>10005279</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 150G</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20040293</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 900G</t>
-  </si>
-  <si>
-    <t>20040296</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 900</t>
-  </si>
-  <si>
-    <t>20040295</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 900G</t>
-  </si>
-  <si>
-    <t>20066494</t>
-  </si>
-  <si>
-    <t>SGM EKSPL5+ MADU 900</t>
-  </si>
-  <si>
-    <t>10005315</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 150G</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20040297</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 1KG</t>
-  </si>
-  <si>
-    <t>20040298</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 1KG</t>
-  </si>
-  <si>
-    <t>20065379</t>
-  </si>
-  <si>
-    <t>SGM SOYA1+ VANL 700G</t>
-  </si>
-  <si>
-    <t>20071686</t>
-  </si>
-  <si>
-    <t>SGM SOYA1+ MADU 700G</t>
+    <t>20055287</t>
+  </si>
+  <si>
+    <t>LACTOGRW PRO1+MDU350</t>
+  </si>
+  <si>
+    <t>20017965</t>
+  </si>
+  <si>
+    <t>LACTOGEN PRO FORM350</t>
+  </si>
+  <si>
+    <t>20017679</t>
+  </si>
+  <si>
+    <t>LACTOGEN PRO LANJ350</t>
+  </si>
+  <si>
+    <t>20113345</t>
+  </si>
+  <si>
+    <t>LACTOGRW PRO1+VAN350</t>
+  </si>
+  <si>
+    <t>10006262</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 750</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>10015652</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ VAN BOX 750</t>
+  </si>
+  <si>
+    <t>10013035</t>
+  </si>
+  <si>
+    <t>DNCOW 3+ MDU BOX 750</t>
+  </si>
+  <si>
+    <t>10015650</t>
+  </si>
+  <si>
+    <t>DNCOW 3+ VAN BOX 750</t>
+  </si>
+  <si>
+    <t>10023780</t>
+  </si>
+  <si>
+    <t>DNCOW 5+ MDU BOX 750</t>
+  </si>
+  <si>
+    <t>10009496</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 350</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>10015653</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ VAN BOX 350</t>
+  </si>
+  <si>
+    <t>10012967</t>
+  </si>
+  <si>
+    <t>DNCOW 3+ MDU BOX 350</t>
+  </si>
+  <si>
+    <t>10015651</t>
+  </si>
+  <si>
+    <t>DNCOW3+ VAN BOX  350</t>
+  </si>
+  <si>
+    <t>20005712</t>
+  </si>
+  <si>
+    <t>DNCOW 5+ VAN BOX 350</t>
+  </si>
+  <si>
+    <t>20138477</t>
+  </si>
+  <si>
+    <t>DANCOW CHO.CR 346.5G</t>
+  </si>
+  <si>
+    <t>10009494</t>
+  </si>
+  <si>
+    <t>DANCOW FORTIGRO 390G</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>10009495</t>
+  </si>
+  <si>
+    <t>DNCW FRTG FL.CRM 390</t>
+  </si>
+  <si>
+    <t>10009493</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 390G</t>
+  </si>
+  <si>
+    <t>10006259</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO ENR 780G</t>
+  </si>
+  <si>
+    <t>10006260</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 780</t>
+  </si>
+  <si>
+    <t>10006258</t>
+  </si>
+  <si>
+    <t>DNCOWFRTGO F.CR 780G</t>
+  </si>
+  <si>
+    <t>20035629</t>
+  </si>
+  <si>
+    <t>BEBELAC 1+VNL BOX350</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20035633</t>
+  </si>
+  <si>
+    <t>BEBELAC3+ VNL BOX350</t>
+  </si>
+  <si>
+    <t>20035635</t>
+  </si>
+  <si>
+    <t>BEBELAC3+ MDU BOX350</t>
+  </si>
+  <si>
+    <t>10025848</t>
+  </si>
+  <si>
+    <t>NTRILON 3 RYL VAN400</t>
   </si>
   <si>
     <t>10010874</t>
@@ -1009,226 +1162,49 @@
     <t>DNCOW 1+ MDU BOX 120</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>10005338</t>
   </si>
   <si>
     <t>DNCOW FRTGO BOX 195G</t>
   </si>
   <si>
-    <t>10010509</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 195G</t>
-  </si>
-  <si>
-    <t>10009494</t>
-  </si>
-  <si>
-    <t>DANCOW FORTIGRO 390G</t>
-  </si>
-  <si>
-    <t>10009495</t>
-  </si>
-  <si>
-    <t>DNCW FRTG FL.CRM 390</t>
-  </si>
-  <si>
-    <t>10009493</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 390G</t>
-  </si>
-  <si>
-    <t>20138477</t>
-  </si>
-  <si>
-    <t>DANCOW CHO.CR 346.5G</t>
-  </si>
-  <si>
-    <t>10006262</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>10015652</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ VAN BOX 750</t>
-  </si>
-  <si>
-    <t>10013035</t>
-  </si>
-  <si>
-    <t>DNCOW 3+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>10015650</t>
-  </si>
-  <si>
-    <t>DNCOW 3+ VAN BOX 750</t>
-  </si>
-  <si>
-    <t>10023780</t>
-  </si>
-  <si>
-    <t>DNCOW 5+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>10009496</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 350</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>10015653</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ VAN BOX 350</t>
-  </si>
-  <si>
-    <t>10012967</t>
-  </si>
-  <si>
-    <t>DNCOW 3+ MDU BOX 350</t>
-  </si>
-  <si>
-    <t>10015651</t>
-  </si>
-  <si>
-    <t>DNCOW3+ VAN BOX  350</t>
-  </si>
-  <si>
-    <t>10023779</t>
-  </si>
-  <si>
-    <t>DNCOW 5+ MDU BOX 350</t>
-  </si>
-  <si>
-    <t>20005712</t>
-  </si>
-  <si>
-    <t>DNCOW 5+ VAN BOX 350</t>
-  </si>
-  <si>
-    <t>10006259</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO ENR 780G</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>10006260</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 780</t>
-  </si>
-  <si>
-    <t>20017965</t>
-  </si>
-  <si>
-    <t>LACTOGEN 1/PRO 350GR</t>
-  </si>
-  <si>
-    <t>20017679</t>
-  </si>
-  <si>
-    <t>LACTOGEN 2 PRO 350GR</t>
-  </si>
-  <si>
-    <t>20055287</t>
-  </si>
-  <si>
-    <t>LACTOGRW3 PRO MDU350</t>
-  </si>
-  <si>
-    <t>20113345</t>
-  </si>
-  <si>
-    <t>LACTOGRW3 PRO VAN350</t>
+    <t>20057224</t>
+  </si>
+  <si>
+    <t>BEBELOVE1 0-6 BOX175</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20045528</t>
+  </si>
+  <si>
+    <t>BEBELOVE2 6-12BOX175</t>
+  </si>
+  <si>
+    <t>20043039</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ MDU BOX175</t>
+  </si>
+  <si>
+    <t>20035626</t>
+  </si>
+  <si>
+    <t>BEBELOVE 1 BOX 350GR</t>
+  </si>
+  <si>
+    <t>20035627</t>
+  </si>
+  <si>
+    <t>BEBELOVE2 6-12BOX350</t>
   </si>
   <si>
     <t>20035631</t>
   </si>
   <si>
     <t>BEBELAC1+ MDU BOX350</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20035629</t>
-  </si>
-  <si>
-    <t>BEBELAC 1+VNL BOX350</t>
-  </si>
-  <si>
-    <t>20035635</t>
-  </si>
-  <si>
-    <t>BEBELAC3+ MDU BOX350</t>
-  </si>
-  <si>
-    <t>20079649</t>
-  </si>
-  <si>
-    <t>BEBELAC GLD3 VAN360</t>
-  </si>
-  <si>
-    <t>10025848</t>
-  </si>
-  <si>
-    <t>NTRILON 3 RYL VAN400</t>
-  </si>
-  <si>
-    <t>20057224</t>
-  </si>
-  <si>
-    <t>BEBELOVE1 0-6 BOX175</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20045528</t>
-  </si>
-  <si>
-    <t>BEBELOVE2 6-12BOX175</t>
-  </si>
-  <si>
-    <t>20043039</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ MDU BOX175</t>
-  </si>
-  <si>
-    <t>20035633</t>
-  </si>
-  <si>
-    <t>BEBELAC3+ VNL BOX350</t>
-  </si>
-  <si>
-    <t>20035626</t>
-  </si>
-  <si>
-    <t>BEBELOVE 1 BOX 350GR</t>
-  </si>
-  <si>
-    <t>20035627</t>
-  </si>
-  <si>
-    <t>BEBELOVE2 6-12BOX350</t>
   </si>
   <si>
     <t>20136285</t>
@@ -1654,7 +1630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1781,15 +1757,15 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -1798,18 +1774,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -1818,18 +1794,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -1838,18 +1814,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1858,10 +1834,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1881,15 +1857,15 @@
         <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1898,18 +1874,18 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1926,10 +1902,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1946,10 +1922,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1961,15 +1937,15 @@
         <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1978,7 +1954,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1998,7 +1974,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -2018,7 +1994,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -2038,18 +2014,18 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -2058,18 +2034,18 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2078,38 +2054,38 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -2118,7 +2094,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2126,10 +2102,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -2138,18 +2114,18 @@
         <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -2158,18 +2134,18 @@
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -2186,10 +2162,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -2201,15 +2177,15 @@
         <v>17</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -2218,18 +2194,18 @@
         <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -2238,7 +2214,7 @@
         <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2246,39 +2222,39 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2286,19 +2262,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2306,19 +2282,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2326,59 +2302,59 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F34" s="1" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2386,19 +2362,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2406,10 +2382,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2418,158 +2394,158 @@
         <v>14</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2578,610 +2554,610 @@
         <v>17</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3195,13 +3171,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3215,13 +3191,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3235,13 +3211,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3255,13 +3231,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3275,13 +3251,13 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3295,13 +3271,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3315,13 +3291,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3335,13 +3311,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3355,13 +3331,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3375,13 +3351,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3395,13 +3371,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3415,13 +3391,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3435,13 +3411,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3455,13 +3431,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3475,13 +3451,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3498,10 +3474,10 @@
         <v>34</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3515,13 +3491,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3535,13 +3511,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3555,13 +3531,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3575,7 +3551,7 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>14</v>
@@ -3595,13 +3571,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3615,10 +3591,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3635,10 +3611,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3655,10 +3631,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3675,7 +3651,7 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>14</v>
@@ -3695,10 +3671,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>168</v>
+        <v>221</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3706,19 +3682,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3735,13 +3711,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3755,10 +3731,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3775,53 +3751,53 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3835,13 +3811,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3855,10 +3831,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3866,62 +3842,62 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3935,13 +3911,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3955,113 +3931,113 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4075,90 +4051,90 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4175,10 +4151,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4195,10 +4171,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4215,10 +4191,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4226,19 +4202,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4246,19 +4222,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4266,19 +4242,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4286,19 +4262,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4315,10 +4291,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4335,10 +4311,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4346,19 +4322,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="E135" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4366,19 +4342,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4386,19 +4362,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4406,19 +4382,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4435,10 +4411,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4446,19 +4422,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4466,19 +4442,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4486,19 +4462,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4506,22 +4482,22 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4535,10 +4511,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4546,19 +4522,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4566,59 +4542,59 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4635,50 +4611,50 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4686,19 +4662,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4706,19 +4682,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4735,10 +4711,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4755,10 +4731,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4766,19 +4742,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4786,19 +4762,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4806,19 +4782,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4826,36 +4802,36 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>4</v>
@@ -4866,16 +4842,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>8</v>
@@ -4886,16 +4862,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>11</v>
@@ -4906,19 +4882,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4926,19 +4902,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4946,22 +4922,22 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4975,10 +4951,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -4986,19 +4962,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5006,19 +4982,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5026,19 +5002,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5046,19 +5022,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5066,19 +5042,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5095,10 +5071,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5106,19 +5082,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5126,19 +5102,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5146,19 +5122,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5166,19 +5142,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5186,19 +5162,19 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5215,10 +5191,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5226,19 +5202,19 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5246,19 +5222,19 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5266,19 +5242,19 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5286,19 +5262,19 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5315,10 +5291,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5335,10 +5311,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5346,59 +5322,59 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5406,101 +5382,21 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F192" s="1" t="s">
         <v>5</v>
       </c>
     </row>
